--- a/data/interview_scores.xlsx
+++ b/data/interview_scores.xlsx
@@ -1,87 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yashw\Desktop\AgenticHR\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AFD2A0-CBED-41DD-A757-A607CE22EB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Candidate Name</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Communication</t>
-  </si>
-  <si>
-    <t>Technical</t>
-  </si>
-  <si>
-    <t>Experience</t>
-  </si>
-  <si>
-    <t>Enthusiasm</t>
-  </si>
-  <si>
-    <t>Response Quality</t>
-  </si>
-  <si>
-    <t>Total Score</t>
-  </si>
-  <si>
-    <t>Recommendation</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>Transcript Path</t>
-  </si>
-  <si>
-    <t>Scored Date</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -96,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -420,55 +420,134 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.21875" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" customWidth="1"/>
-    <col min="13" max="13" width="29.109375" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Candidate Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Enthusiasm</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Response Quality</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Total Score</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Transcript Path</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Scored Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Rahul Sharma</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>yashwanthdevangam@gmail.com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Consider</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Rahul's responses were often unclear and lacked detail. He struggled to articulate his skills and experiences, and his answers were often incomplete. While he showed some enthusiasm for the role, his communication skills and technical knowledge were lacking.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>C:\Users\yashw\Desktop\AgenticHR\unverified_transcripts\Rahul_Sharma_20260126_181038.txt</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-03-09 20:06:03</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/interview_scores.xlsx
+++ b/data/interview_scores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,61 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>2026-03-09 20:06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rahul Sharma Monday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>yashwanthdevangam@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>35</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Do Not Recommend</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>The candidate struggled to articulate his responses, lacked relevant experience, and demonstrated limited technical knowledge. His communication skills were also a concern.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>C:\Users\yashw\Desktop\AgenticHR\unverified_transcripts\Rahul_Sharma_20260126_181038.txt</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-03-13 19:57:24</t>
         </is>
       </c>
     </row>
